--- a/Audit/JJ_PM_SC03_요구사항추적표_v1.3_20261028_이노팸.xlsx
+++ b/Audit/JJ_PM_SC03_요구사항추적표_v1.3_20261028_이노팸.xlsx
@@ -15,9 +15,6 @@
     <definedName name="_kwy1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="_Order1" hidden="1">255</definedName>
     <definedName name="_Order2" hidden="1">255</definedName>
-    <definedName name="_Table1_In1" hidden="1">#REF!</definedName>
-    <definedName name="_Table1_Out" hidden="1">#REF!</definedName>
-    <definedName name="AA" hidden="1">#REF!</definedName>
     <definedName name="cwe" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="D" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="DJDJDJDJ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
@@ -27,7 +24,6 @@
     <definedName name="dkw" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="dsfga" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="er" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="FF" hidden="1">#REF!</definedName>
     <definedName name="fkwheku" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="gfdsdfg" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="H" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
@@ -46,12 +42,8 @@
     <definedName name="kwy" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="PERT" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="qq" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="rr" hidden="1">#REF!</definedName>
-    <definedName name="RRR" hidden="1">#REF!</definedName>
     <definedName name="s" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="SS" hidden="1">#REF!</definedName>
     <definedName name="TOTAL" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="tt" hidden="1">#REF!</definedName>
     <definedName name="vbkjwhe" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="vdwf" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="vewtf" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -92,12 +84,10 @@
     <definedName name="wrn.aaa." hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="wrn.TEST." hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="wte" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ww" hidden="1">#REF!</definedName>
     <definedName name="ㄱ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="ㄱㅎㄷㄱㅎ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="가" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="공사설명서" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄴ" hidden="1">#REF!</definedName>
     <definedName name="ㄴㄴㄱ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㄴㄹ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㄴ아러" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -109,16 +99,13 @@
     <definedName name="ㄹㅇㅁㄴㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="라" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㄻㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅁ" hidden="1">#REF!</definedName>
     <definedName name="ㅁㄻㄴㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="ㅁㅁㅁ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="마" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅂ" hidden="1">#REF!</definedName>
     <definedName name="ㅂㅂ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="바" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="변경내역" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="보" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅅㅅㅅ" hidden="1">#REF!</definedName>
     <definedName name="사" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="수" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="수정" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -142,7 +129,6 @@
     <definedName name="아ㅓㅗㄹ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="아ㅣㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="아ㅣㅈㅂ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="이름" hidden="1">#REF!</definedName>
     <definedName name="일일대가1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="잊" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -180,9 +166,6 @@
     <definedName name="ㅣ젇" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'표지'!$A$1:$D$30</definedName>
     <definedName name="_kwy1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="_Table1_In1" localSheetId="2" hidden="1">#REF!</definedName>
-    <definedName name="_Table1_Out" localSheetId="2" hidden="1">#REF!</definedName>
-    <definedName name="AA" localSheetId="2" hidden="1">#REF!</definedName>
     <definedName name="cwe" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="D" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="DJDJDJDJ" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
@@ -210,10 +193,7 @@
     <definedName name="kwy" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="PERT" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="qq" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="rr" localSheetId="2" hidden="1">#REF!</definedName>
-    <definedName name="RRR" localSheetId="2" hidden="1">#REF!</definedName>
     <definedName name="s" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="SS" localSheetId="2" hidden="1">#REF!</definedName>
     <definedName name="TOTAL" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="vbkjwhe" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="vdwf" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -300,7 +280,6 @@
     <definedName name="아ㅓㅗㄹ" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="아ㅣㅈ" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="아ㅣㅈㅂ" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="이름" localSheetId="2" hidden="1">#REF!</definedName>
     <definedName name="일일대가1" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="잊" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅈ" localSheetId="2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -340,9 +319,6 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'요구사항추적표(기능)'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'요구사항추적표(기능)'!$B$1:$S$59</definedName>
     <definedName name="_kwy1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="_Table1_In1" localSheetId="3" hidden="1">#REF!</definedName>
-    <definedName name="_Table1_Out" localSheetId="3" hidden="1">#REF!</definedName>
-    <definedName name="AA" localSheetId="3" hidden="1">#REF!</definedName>
     <definedName name="cwe" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="D" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="DJDJDJDJ" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
@@ -370,10 +346,7 @@
     <definedName name="kwy" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="PERT" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="qq" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="rr" localSheetId="3" hidden="1">#REF!</definedName>
-    <definedName name="RRR" localSheetId="3" hidden="1">#REF!</definedName>
     <definedName name="s" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="SS" localSheetId="3" hidden="1">#REF!</definedName>
     <definedName name="TOTAL" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="vbkjwhe" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="vdwf" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -460,7 +433,6 @@
     <definedName name="아ㅓㅗㄹ" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="아ㅣㅈ" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="아ㅣㅈㅂ" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="이름" localSheetId="3" hidden="1">#REF!</definedName>
     <definedName name="일일대가1" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="잊" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅈ" localSheetId="3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>

--- a/Audit/JJ_PM_SC03_요구사항추적표_v1.3_20261028_이노팸.xlsx
+++ b/Audit/JJ_PM_SC03_요구사항추적표_v1.3_20261028_이노팸.xlsx
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>화면설계서 v1.5 검수본 반영: 메뉴 명칭 현행화(불법 주차 집중 구역 분석·정책 효과 시뮬레이션·구역추천·대시보드), 격자 크기(100m~1km), 예측 기간 삭제, 알림 기준 설정 팝업, 구역추천 해결방안 현행화, AI 모델 표기(Gemma)</t>
+          <t>화면설계서 v1.5 검수본 반영: 메뉴 명칭 현행화(불법 주차 집중 구역 분석·정책 효과 시뮬레이션·구역추천·대시보드), 격자 크기(100m~1km), 예측 기간 삭제, 알림 기준 설정 팝업, 구역추천 해결방안 현행화, AI 모델 표기(Gemma), 민원현황 히트맵 표현 전환·AI 조례 응답 방식 현행화</t>
         </is>
       </c>
       <c r="D6" s="32" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>○ 민원 발생 현황·패턴을 제주 전역 히트맵과 읍·면·동 집계 순위로 시각화하여 '민원현황' 화면에 구현
+          <t>○ 민원 발생 현황·패턴을 제주 전역 히트맵(민원 건수 밀도)과 읍·면·동 집계 순위로 시각화하여 '민원현황' 화면에 구현 — 민원 다발·단속 집중 레이어는 읍면동(폴리곤) ↔ 히트맵 표현 전환 지원
 ○ 읍·면·동 비교카드(건수·증감율·유형 세분화)로 '대시보드'에 구현</t>
         </is>
       </c>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>○ 민원 다발지역·단속 집중지역·수요 부족지역을 레이어 선택 기반 히트맵과 KPI 카드·범례로 GIS 시각화하여 '민원현황' 화면에 구현</t>
+          <t>○ 민원 다발지역·단속 집중지역·수요 부족지역을 레이어 선택 기반으로 GIS 시각화하여 '민원현황' 화면에 구현 — 민원 다발·단속 집중 레이어는 읍면동(폴리곤) ↔ 히트맵(밀도) 표현 전환, 등급·그라데이션 범례 제공</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>○ sLLM·RAG 기반 정책문서·조례 검색 및 행정 Q&amp;A·보고서 작성 지원을 'AI 어시스턴트'로 구현</t>
+          <t>○ sLLM·RAG 기반 정책문서·조례 검색 및 행정 Q&amp;A·보고서 작성 지원을 'AI 어시스턴트'로 구현 — 조례 질의 시 조례명·관련 조문 발췌로 응답</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">

--- a/Audit/JJ_PM_SC03_요구사항추적표_v1.3_20261028_이노팸.xlsx
+++ b/Audit/JJ_PM_SC03_요구사항추적표_v1.3_20261028_이노팸.xlsx
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>화면설계서 v1.5 검수본 반영: 메뉴 명칭 현행화(불법 주차 집중 구역 분석·정책 효과 시뮬레이션·구역추천·대시보드), 격자 크기(100m~1km), 예측 기간 삭제, 알림 기준 설정 팝업, 구역추천 해결방안 현행화, AI 모델 표기(Gemma), 민원현황 히트맵 표현 전환·AI 조례 응답 방식 현행화</t>
+          <t>화면설계서 v1.5 검수본 반영: 메뉴 명칭 현행화(불법 주차 집중 구역 분석·정책 효과 시뮬레이션·구역추천·대시보드), 격자 크기(100m~1km), 예측 기간 삭제, 알림 기준 설정 팝업, 구역추천 해결방안 현행화, AI 모델 표기(Gemma)</t>
         </is>
       </c>
       <c r="D6" s="32" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>○ 민원 발생 현황·패턴을 제주 전역 히트맵(민원 건수 밀도)과 읍·면·동 집계 순위로 시각화하여 '민원현황' 화면에 구현 — 민원 다발·단속 집중 레이어는 읍면동(폴리곤) ↔ 히트맵 표현 전환 지원
+          <t>○ 민원 발생 현황·패턴을 제주 전역 히트맵과 읍·면·동 집계 순위로 시각화하여 '민원현황' 화면에 구현
 ○ 읍·면·동 비교카드(건수·증감율·유형 세분화)로 '대시보드'에 구현</t>
         </is>
       </c>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>○ 민원 다발지역·단속 집중지역·수요 부족지역을 레이어 선택 기반으로 GIS 시각화하여 '민원현황' 화면에 구현 — 민원 다발·단속 집중 레이어는 읍면동(폴리곤) ↔ 히트맵(밀도) 표현 전환, 등급·그라데이션 범례 제공</t>
+          <t>○ 민원 다발지역·단속 집중지역·수요 부족지역을 레이어 선택 기반 히트맵과 KPI 카드·범례로 GIS 시각화하여 '민원현황' 화면에 구현</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>○ sLLM·RAG 기반 정책문서·조례 검색 및 행정 Q&amp;A·보고서 작성 지원을 'AI 어시스턴트'로 구현 — 조례 질의 시 조례명·관련 조문 발췌로 응답</t>
+          <t>○ sLLM·RAG 기반 정책문서·조례 검색 및 행정 Q&amp;A·보고서 작성 지원을 'AI 어시스턴트'로 구현</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
